--- a/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
+++ b/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\AVLo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B446D3AE-B87D-4E62-AC29-BC99054FBCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA62E737-16DD-479C-935A-B97ED393513D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BTS NTS Modal Profile Data" sheetId="3" r:id="rId2"/>
-    <sheet name="AVLo-passengers" sheetId="2" r:id="rId3"/>
-    <sheet name="AVLo-freight" sheetId="4" r:id="rId4"/>
+    <sheet name="SYAVLo-passengers" sheetId="2" r:id="rId3"/>
+    <sheet name="SYAVLo-freight" sheetId="4" r:id="rId4"/>
+    <sheet name="AVLo-passengers" sheetId="5" r:id="rId5"/>
+    <sheet name="AVLo-freight" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="Eno_TM">'[1]1997  Table 1a Modified'!#REF!</definedName>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="116">
   <si>
     <t>AVLo Average Vehicle Loading</t>
   </si>
@@ -1467,7 +1469,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Rail shipments 93-97"/>
@@ -1548,9 +1550,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1588,9 +1590,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1623,26 +1625,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1675,26 +1660,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1869,10 +1837,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" customWidth="1"/>
-    <col min="2" max="2" width="85.08984375" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="85.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2139,11 +2107,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="73.6328125" customWidth="1"/>
+    <col min="1" max="1" width="73.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="102.26953125" customWidth="1"/>
+    <col min="3" max="3" width="102.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2662,275 +2630,30 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="43.5">
+    <row r="1" spans="1:2" ht="45">
       <c r="A1" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B1" s="5">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="5">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="5">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="H1" s="5">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="5">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="5">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-      <c r="N1" s="5">
-        <v>2027</v>
-      </c>
-      <c r="O1" s="1">
-        <v>2028</v>
-      </c>
-      <c r="P1" s="5">
-        <v>2029</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>2030</v>
-      </c>
-      <c r="R1" s="5">
-        <v>2031</v>
-      </c>
-      <c r="S1" s="1">
-        <v>2032</v>
-      </c>
-      <c r="T1" s="5">
-        <v>2033</v>
-      </c>
-      <c r="U1" s="1">
-        <v>2034</v>
-      </c>
-      <c r="V1" s="5">
-        <v>2035</v>
-      </c>
-      <c r="W1" s="1">
-        <v>2036</v>
-      </c>
-      <c r="X1" s="5">
-        <v>2037</v>
-      </c>
-      <c r="Y1" s="1">
-        <v>2038</v>
-      </c>
-      <c r="Z1" s="5">
-        <v>2039</v>
-      </c>
-      <c r="AA1" s="1">
-        <v>2040</v>
-      </c>
-      <c r="AB1" s="5">
-        <v>2041</v>
-      </c>
-      <c r="AC1" s="1">
-        <v>2042</v>
-      </c>
-      <c r="AD1" s="5">
-        <v>2043</v>
-      </c>
-      <c r="AE1" s="1">
-        <v>2044</v>
-      </c>
-      <c r="AF1" s="5">
-        <v>2045</v>
-      </c>
-      <c r="AG1" s="1">
-        <v>2046</v>
-      </c>
-      <c r="AH1" s="5">
-        <v>2047</v>
-      </c>
-      <c r="AI1" s="1">
-        <v>2048</v>
-      </c>
-      <c r="AJ1" s="5">
-        <v>2049</v>
-      </c>
-      <c r="AK1" s="1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="7">
         <v>1.67</v>
       </c>
-      <c r="C2" s="7">
-        <f>$B2</f>
-        <v>1.67</v>
-      </c>
-      <c r="D2" s="7">
-        <f t="shared" ref="D2:AK7" si="0">$B2</f>
-        <v>1.67</v>
-      </c>
-      <c r="E2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="F2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="G2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="H2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="I2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="J2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="K2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="L2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="M2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="N2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="O2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="P2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="Q2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="R2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="S2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="T2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="U2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="V2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="W2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="X2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="Y2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="Z2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AA2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AB2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AC2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AD2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AE2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AF2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AG2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AH2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AI2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AJ2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AK2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2938,148 +2661,8 @@
         <f>'BTS NTS Modal Profile Data'!B14</f>
         <v>21.196137258578663</v>
       </c>
-      <c r="C3" s="7">
-        <f t="shared" ref="C3:R7" si="1">$B3</f>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="D3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="E3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="F3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="G3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="H3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="I3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="J3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="K3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="L3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="M3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="N3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="O3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="P3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="Q3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="R3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="S3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="T3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="U3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="V3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="W3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="X3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="Y3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="Z3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AA3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AB3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AC3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AD3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AE3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AF3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AG3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AH3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AI3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AJ3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AK3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -3087,148 +2670,8 @@
         <f>'BTS NTS Modal Profile Data'!B8</f>
         <v>111.39416306433705</v>
       </c>
-      <c r="C4" s="7">
-        <f t="shared" si="1"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="D4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="E4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="F4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="G4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="H4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="I4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="J4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="K4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="L4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="M4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="N4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="O4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="P4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="Q4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="R4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="S4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="T4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="U4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="V4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="W4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="X4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="Y4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="Z4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AA4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AB4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AC4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AD4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AE4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AF4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AG4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AH4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AI4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AJ4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AK4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -3236,441 +2679,21 @@
         <f>'BTS NTS Modal Profile Data'!B37</f>
         <v>486.56731685074101</v>
       </c>
-      <c r="C5" s="7">
-        <f t="shared" si="1"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="D5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="Q5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="S5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="T5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="W5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="X5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="Y5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="Z5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AA5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AB5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AC5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AD5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AE5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AF5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AG5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AH5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AI5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AJ5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AK5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="R6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="T6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="V6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="W6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="7">
         <f>'BTS NTS Modal Profile Data'!B60</f>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="C7" s="7">
-        <f t="shared" si="1"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="D7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="E7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="F7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="H7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="K7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="L7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="M7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="N7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="O7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="P7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="Q7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="R7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="S7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="T7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="U7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="V7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="W7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="X7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="Y7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="Z7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AA7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AB7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AC7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AD7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AE7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AF7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AG7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AH7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AI7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AJ7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AK7" s="7">
-        <f t="shared" si="0"/>
         <v>1.2700756740871355</v>
       </c>
     </row>
@@ -3684,411 +2707,37 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" ht="43.5">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="45">
       <c r="A1" s="16" t="s">
         <v>112</v>
       </c>
       <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2027</v>
-      </c>
-      <c r="N1" s="1">
-        <v>2028</v>
-      </c>
-      <c r="O1" s="1">
-        <v>2029</v>
-      </c>
-      <c r="P1" s="1">
-        <v>2030</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>2031</v>
-      </c>
-      <c r="R1" s="1">
-        <v>2032</v>
-      </c>
-      <c r="S1" s="1">
-        <v>2033</v>
-      </c>
-      <c r="T1" s="1">
-        <v>2034</v>
-      </c>
-      <c r="U1" s="1">
-        <v>2035</v>
-      </c>
-      <c r="V1" s="1">
-        <v>2036</v>
-      </c>
-      <c r="W1" s="1">
-        <v>2037</v>
-      </c>
-      <c r="X1" s="1">
-        <v>2038</v>
-      </c>
-      <c r="Y1" s="1">
-        <v>2039</v>
-      </c>
-      <c r="Z1" s="1">
-        <v>2040</v>
-      </c>
-      <c r="AA1" s="1">
-        <v>2041</v>
-      </c>
-      <c r="AB1" s="1">
-        <v>2042</v>
-      </c>
-      <c r="AC1" s="1">
-        <v>2043</v>
-      </c>
-      <c r="AD1" s="1">
-        <v>2044</v>
-      </c>
-      <c r="AE1" s="1">
-        <v>2045</v>
-      </c>
-      <c r="AF1" s="1">
-        <v>2046</v>
-      </c>
-      <c r="AG1" s="1">
-        <v>2047</v>
-      </c>
-      <c r="AH1" s="1">
-        <v>2048</v>
-      </c>
-      <c r="AI1" s="1">
-        <v>2049</v>
-      </c>
-      <c r="AJ1" s="1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="14">
         <v>1</v>
       </c>
-      <c r="C2">
-        <f t="shared" ref="C2:R7" si="0">$B2</f>
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <f t="shared" ref="D2:AJ7" si="1">$B2</f>
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="W2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="X2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AA2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AC2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AE2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AF2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AG2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AH2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AI2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AJ2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6">
         <v>16</v>
       </c>
-      <c r="C3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="H3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="I3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="J3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="K3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="M3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="N3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="O3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="P3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="R3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="S3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="T3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="U3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="V3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="W3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="X3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="Y3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="Z3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AA3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AB3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AC3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AD3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AE3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AF3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AG3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AH3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AI3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="AJ3">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -4096,144 +2745,8 @@
         <f>'BTS NTS Modal Profile Data'!B9</f>
         <v>41.989116133258747</v>
       </c>
-      <c r="C4" s="6">
-        <f t="shared" si="0"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="D4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="E4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="F4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="G4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="H4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="I4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="J4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="K4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="L4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="M4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="N4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="O4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="P4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="Q4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="R4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="S4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="T4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="U4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="V4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="W4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="X4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="Y4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="Z4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AA4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AB4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AC4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AD4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AE4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AF4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AG4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AH4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AI4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-      <c r="AJ4" s="6">
-        <f t="shared" si="1"/>
-        <v>41.989116133258747</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -4241,144 +2754,8 @@
         <f>'BTS NTS Modal Profile Data'!B19</f>
         <v>3512.35916421195</v>
       </c>
-      <c r="C5" s="6">
-        <f t="shared" si="0"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="E5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="F5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="G5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="H5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="I5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="J5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="K5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="L5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="M5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="N5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="O5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="P5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="Q5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="R5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="S5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="T5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="U5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="V5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="W5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="X5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="Y5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="Z5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AA5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AB5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AC5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AD5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AE5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AF5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AG5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AH5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AI5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-      <c r="AJ5" s="6">
-        <f t="shared" si="1"/>
-        <v>3512.35916421195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -4386,284 +2763,1731 @@
         <f>'BTS NTS Modal Profile Data'!B55</f>
         <v>1974.4736422180429</v>
       </c>
-      <c r="C6" s="6">
-        <f t="shared" si="0"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="E6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="F6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="G6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="H6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="I6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="J6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="K6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="L6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="M6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="N6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="O6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="P6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="Q6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="R6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="S6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="T6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="U6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="V6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="W6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="Y6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="Z6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AA6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AB6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AC6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AD6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AE6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AF6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AG6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AH6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AI6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-      <c r="AJ6" s="6">
-        <f t="shared" si="1"/>
-        <v>1974.4736422180429</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A6C762-134A-444D-BF60-BC99F3DFC165}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AE7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" ht="45">
+      <c r="A1" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="5">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="5">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="5">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="5">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="5">
+        <v>2027</v>
+      </c>
+      <c r="I1" s="5">
+        <v>2028</v>
+      </c>
+      <c r="J1" s="5">
+        <v>2029</v>
+      </c>
+      <c r="K1" s="5">
+        <v>2030</v>
+      </c>
+      <c r="L1" s="5">
+        <v>2031</v>
+      </c>
+      <c r="M1" s="5">
+        <v>2032</v>
+      </c>
+      <c r="N1" s="5">
+        <v>2033</v>
+      </c>
+      <c r="O1" s="5">
+        <v>2034</v>
+      </c>
+      <c r="P1" s="5">
+        <v>2035</v>
+      </c>
+      <c r="Q1" s="5">
+        <v>2036</v>
+      </c>
+      <c r="R1" s="5">
+        <v>2037</v>
+      </c>
+      <c r="S1" s="5">
+        <v>2038</v>
+      </c>
+      <c r="T1" s="5">
+        <v>2039</v>
+      </c>
+      <c r="U1" s="5">
+        <v>2040</v>
+      </c>
+      <c r="V1" s="5">
+        <v>2041</v>
+      </c>
+      <c r="W1" s="5">
+        <v>2042</v>
+      </c>
+      <c r="X1" s="5">
+        <v>2043</v>
+      </c>
+      <c r="Y1" s="5">
+        <v>2044</v>
+      </c>
+      <c r="Z1" s="5">
+        <v>2045</v>
+      </c>
+      <c r="AA1" s="5">
+        <v>2046</v>
+      </c>
+      <c r="AB1" s="5">
+        <v>2047</v>
+      </c>
+      <c r="AC1" s="5">
+        <v>2048</v>
+      </c>
+      <c r="AD1" s="5">
+        <v>2049</v>
+      </c>
+      <c r="AE1" s="5">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1.67</v>
+      </c>
+      <c r="C2" s="7">
+        <f>$B2</f>
+        <v>1.67</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" ref="D2:AE7" si="0">$B2</f>
+        <v>1.67</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="G2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="H2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="I2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="J2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="K2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="L2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="M2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="P2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="Q2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="R2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="S2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="T2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="U2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="V2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="W2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="X2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="Y2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="Z2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AA2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AB2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AC2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AD2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AE2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="9">
+        <f>'BTS NTS Modal Profile Data'!B14</f>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="C3" s="7">
+        <f t="shared" ref="C3:R7" si="1">$B3</f>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="E3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="F3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="J3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="P3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="Q3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="R3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="S3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="T3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="U3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="V3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="W3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="X3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="Y3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="Z3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AA3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AB3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AC3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AD3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AE3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="9">
+        <f>'BTS NTS Modal Profile Data'!B8</f>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="1"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="P4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="R4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="S4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="T4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="U4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="V4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="W4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="X4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="Y4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="Z4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AA4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AB4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AC4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AD4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AE4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9">
+        <f>'BTS NTS Modal Profile Data'!B37</f>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="C5" s="7">
+        <f t="shared" si="1"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="R5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="S5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="T5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="U5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="V5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="W5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="X5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="Y5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="Z5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AA5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AB5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AC5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AD5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AE5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7">
+        <f>'BTS NTS Modal Profile Data'!B60</f>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="C7" s="7">
+        <f t="shared" si="1"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="R7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="S7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="T7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="U7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="V7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="W7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="X7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="Y7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="Z7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AA7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AB7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AC7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AD7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AE7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87475B98-F0F0-452D-A62B-4E672A3FB155}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AE7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" s="1" customFormat="1" ht="45">
+      <c r="A1" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2031</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2033</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2037</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2039</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="V1" s="1">
+        <v>2041</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="X1" s="1">
+        <v>2043</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:F7" si="0">$B2</f>
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <f>$B2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="K3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="M3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="N3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="O3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="P3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="Q3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="R3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="S3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="T3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="U3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="V3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="W3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="X3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="Y3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="Z3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="AA3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="AB3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="AC3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="AD3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+      <c r="AE3">
+        <f>$B3</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6">
+        <f>'BTS NTS Modal Profile Data'!B9</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="C4" s="6">
+        <f t="shared" si="0"/>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" si="0"/>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" si="0"/>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="0"/>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="G4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="H4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="I4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="J4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="K4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="L4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="M4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="N4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="O4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="P4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="Q4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="R4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="S4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="T4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="U4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="V4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="W4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="X4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="Y4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="Z4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="AA4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="AB4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="AC4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="AD4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+      <c r="AE4" s="6">
+        <f>$B4</f>
+        <v>41.989116133258747</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6">
+        <f>'BTS NTS Modal Profile Data'!B19</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="C5" s="6">
+        <f t="shared" si="0"/>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="0"/>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="0"/>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="G5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="H5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="I5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="J5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="K5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="L5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="M5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="N5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="O5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="P5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="Q5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="R5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="S5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="T5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="U5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="V5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="W5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="X5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="Y5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="Z5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="AA5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="AB5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="AC5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="AD5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+      <c r="AE5" s="6">
+        <f>$B5</f>
+        <v>3512.35916421195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'BTS NTS Modal Profile Data'!B55</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="C6" s="6">
+        <f t="shared" si="0"/>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="0"/>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="0"/>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="G6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="H6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="I6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="J6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="K6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="L6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="M6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="N6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="O6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="P6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="Q6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="R6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="S6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="T6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="U6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="V6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="W6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="X6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="Y6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="Z6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AA6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AB6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AC6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AD6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+      <c r="AE6" s="6">
+        <f>$B6</f>
+        <v>1974.4736422180429</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
       <c r="C7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="H7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="M7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>0</v>
       </c>
     </row>
